--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Alva Danielsson, Alva Danielsson, Alva Danielsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92378</v>
+        <v>92379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92379</v>
+        <v>92385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92385</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92391</v>
+        <v>92404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92404</v>
+        <v>92406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92406</v>
+        <v>92409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92409</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92420</v>
+        <v>92423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92423</v>
+        <v>92425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92425</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92442</v>
+        <v>92443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92443</v>
+        <v>92446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92446</v>
+        <v>92450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
